--- a/Spark/Data/Simulated/Bruno/first simulations/comparison_table_SIM2.xlsx
+++ b/Spark/Data/Simulated/Bruno/first simulations/comparison_table_SIM2.xlsx
@@ -401,16 +401,16 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7212</v>
+        <v>0.576083333333333</v>
       </c>
       <c r="D2" t="n">
-        <v>0.740196781245307</v>
+        <v>0.594920533752134</v>
       </c>
       <c r="E2" t="n">
-        <v>0.689823904370416</v>
+        <v>0.5444663719028</v>
       </c>
       <c r="F2" t="n">
-        <v>0.260240981660521</v>
+        <v>0.400375608113449</v>
       </c>
     </row>
     <row r="3">
@@ -421,16 +421,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7164</v>
+        <v>0.572833333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>0.731687156395326</v>
+        <v>0.587161502966469</v>
       </c>
       <c r="E3" t="n">
-        <v>0.689615075880487</v>
+        <v>0.547430254855984</v>
       </c>
       <c r="F3" t="n">
-        <v>0.314074237735059</v>
+        <v>0.451572166216913</v>
       </c>
     </row>
     <row r="4">
@@ -441,16 +441,16 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>0.722866666666667</v>
+        <v>0.563066666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>0.736862353395344</v>
+        <v>0.578417388215933</v>
       </c>
       <c r="E4" t="n">
-        <v>0.697039578299827</v>
+        <v>0.537724403122389</v>
       </c>
       <c r="F4" t="n">
-        <v>0.27708634210852</v>
+        <v>0.437344782216878</v>
       </c>
     </row>
     <row r="5">
@@ -461,16 +461,16 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7529</v>
+        <v>0.594733333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>0.790634227658388</v>
+        <v>0.627512236814509</v>
       </c>
       <c r="E5" t="n">
-        <v>0.705503348604031</v>
+        <v>0.553244641763367</v>
       </c>
       <c r="F5" t="n">
-        <v>0.205108784440059</v>
+        <v>0.369245661306388</v>
       </c>
     </row>
     <row r="6">
@@ -481,16 +481,16 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>0.754883333333333</v>
+        <v>0.59245</v>
       </c>
       <c r="D6" t="n">
-        <v>0.793119388676666</v>
+        <v>0.625276147854893</v>
       </c>
       <c r="E6" t="n">
-        <v>0.706152968699268</v>
+        <v>0.550980479665029</v>
       </c>
       <c r="F6" t="n">
-        <v>0.289721660000934</v>
+        <v>0.448800587172745</v>
       </c>
     </row>
     <row r="7">
@@ -501,16 +501,16 @@
         <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>0.75655</v>
+        <v>0.601966666666667</v>
       </c>
       <c r="D7" t="n">
-        <v>0.794826229053023</v>
+        <v>0.63321891045744</v>
       </c>
       <c r="E7" t="n">
-        <v>0.708020806642776</v>
+        <v>0.561924908521372</v>
       </c>
       <c r="F7" t="n">
-        <v>0.242824260067734</v>
+        <v>0.39657619029608</v>
       </c>
     </row>
     <row r="8">
@@ -521,16 +521,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.729816666666667</v>
+        <v>0.56325</v>
       </c>
       <c r="D8" t="n">
-        <v>0.751862714754268</v>
+        <v>0.581685907543249</v>
       </c>
       <c r="E8" t="n">
-        <v>0.698122278068932</v>
+        <v>0.536832586544457</v>
       </c>
       <c r="F8" t="n">
-        <v>0.243271634400263</v>
+        <v>0.41556445074253</v>
       </c>
     </row>
     <row r="9">
@@ -541,16 +541,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.734083333333333</v>
+        <v>0.5952</v>
       </c>
       <c r="D9" t="n">
-        <v>0.757013228725506</v>
+        <v>0.614635586100845</v>
       </c>
       <c r="E9" t="n">
-        <v>0.700406922182407</v>
+        <v>0.567038043332379</v>
       </c>
       <c r="F9" t="n">
-        <v>0.300842062721306</v>
+        <v>0.433559293213165</v>
       </c>
     </row>
     <row r="10">
@@ -561,16 +561,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7383</v>
+        <v>0.592466666666667</v>
       </c>
       <c r="D10" t="n">
-        <v>0.762075620563701</v>
+        <v>0.612204714907935</v>
       </c>
       <c r="E10" t="n">
-        <v>0.703711281418849</v>
+        <v>0.563592745092759</v>
       </c>
       <c r="F10" t="n">
-        <v>0.261220948641257</v>
+        <v>0.407637852397693</v>
       </c>
     </row>
   </sheetData>
